--- a/main/ExamQuestions_14.xlsx
+++ b/main/ExamQuestions_14.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GEO309\main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GEO302\main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6B7E93B-8B4F-4765-86C3-ED5573E923AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E858776B-B92A-47CC-8B7B-8723398E24BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2528" yWindow="4125" windowWidth="21600" windowHeight="11355" xr2:uid="{7B30B9D5-F944-4DC7-BB71-4FEBCEA1AEDA}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{7B30B9D5-F944-4DC7-BB71-4FEBCEA1AEDA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,12 +28,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
     <t>What is overexploitation?</t>
-  </si>
-  <si>
-    <t>What is habitat lost?</t>
   </si>
 </sst>
 </file>
@@ -410,12 +407,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A2">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="B2" s="1"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B4" s="1"/>
